--- a/Team-Data/2007-08/1-13-2007-08.xlsx
+++ b/Team-Data/2007-08/1-13-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" t="n">
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.485</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="J2" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M2" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>0.317</v>
+        <v>0.311</v>
       </c>
       <c r="O2" t="n">
         <v>22.3</v>
       </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.769</v>
+        <v>0.766</v>
       </c>
       <c r="R2" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S2" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="T2" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="U2" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V2" t="n">
         <v>15.6</v>
@@ -721,37 +788,37 @@
         <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y2" t="n">
         <v>5.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB2" t="n">
-        <v>95</v>
+        <v>94.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.6</v>
+        <v>-1.3</v>
       </c>
       <c r="AD2" t="n">
         <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
         <v>28</v>
@@ -760,7 +827,7 @@
         <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL2" t="n">
         <v>30</v>
@@ -778,22 +845,22 @@
         <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -811,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>11.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
         <v>25</v>
@@ -948,7 +1015,7 @@
         <v>9</v>
       </c>
       <c r="AM3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN3" t="n">
         <v>5</v>
@@ -960,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -969,10 +1036,10 @@
         <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
@@ -987,13 +1054,13 @@
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
         <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1121,7 +1188,7 @@
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
@@ -1133,7 +1200,7 @@
         <v>17</v>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
         <v>16</v>
@@ -1166,7 +1233,7 @@
         <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
@@ -1175,7 +1242,7 @@
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J5" t="n">
         <v>85.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.417</v>
+        <v>0.419</v>
       </c>
       <c r="L5" t="n">
         <v>5.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.328</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P5" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0.758</v>
@@ -1252,40 +1319,40 @@
         <v>14.2</v>
       </c>
       <c r="S5" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T5" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U5" t="n">
         <v>21.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
         <v>21.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.7</v>
+        <v>-3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1294,10 +1361,10 @@
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1312,16 +1379,16 @@
         <v>24</v>
       </c>
       <c r="AM5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ5" t="n">
         <v>14</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1339,16 +1406,16 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
         <v>13</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>-2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
         <v>16</v>
@@ -1497,10 +1564,10 @@
         <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1539,7 +1606,7 @@
         <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
         <v>18</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -1691,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>10</v>
@@ -1700,7 +1767,7 @@
         <v>13</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,13 +1776,13 @@
         <v>28</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1870,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -1935,43 +2002,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
         <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.737</v>
+        <v>0.757</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="J9" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K9" t="n">
-        <v>0.46</v>
+        <v>0.464</v>
       </c>
       <c r="L9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M9" t="n">
         <v>16.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.365</v>
       </c>
       <c r="O9" t="n">
         <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0.769</v>
@@ -1980,19 +2047,19 @@
         <v>11.4</v>
       </c>
       <c r="S9" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T9" t="n">
         <v>40.9</v>
       </c>
       <c r="U9" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="V9" t="n">
         <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X9" t="n">
         <v>5.2</v>
@@ -2001,19 +2068,19 @@
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,25 +2092,25 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
@@ -2061,19 +2128,19 @@
         <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY9" t="n">
         <v>2</v>
@@ -2082,10 +2149,10 @@
         <v>10</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10" t="n">
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.579</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
@@ -2135,37 +2202,37 @@
         <v>40.2</v>
       </c>
       <c r="J10" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="K10" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.35</v>
+        <v>0.354</v>
       </c>
       <c r="O10" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P10" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.737</v>
+        <v>0.742</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U10" t="n">
         <v>22.8</v>
@@ -2174,13 +2241,13 @@
         <v>13.9</v>
       </c>
       <c r="W10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X10" t="n">
         <v>4.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z10" t="n">
         <v>23.2</v>
@@ -2192,13 +2259,13 @@
         <v>108.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
         <v>10</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2225,16 +2292,16 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
         <v>5</v>
@@ -2243,25 +2310,25 @@
         <v>19</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA10" t="n">
         <v>12</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
         <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.526</v>
+        <v>0.541</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J11" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L11" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O11" t="n">
         <v>16.4</v>
@@ -2338,19 +2405,19 @@
         <v>22.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="R11" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S11" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T11" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V11" t="n">
         <v>15.1</v>
@@ -2362,7 +2429,7 @@
         <v>5.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z11" t="n">
         <v>19.9</v>
@@ -2371,34 +2438,34 @@
         <v>20.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ11" t="n">
         <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
         <v>12</v>
@@ -2407,7 +2474,7 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO11" t="n">
         <v>27</v>
@@ -2434,22 +2501,22 @@
         <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
         <v>3</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
         <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC11" t="n">
         <v>12</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
         <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.436</v>
+        <v>0.447</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,10 +2566,10 @@
         <v>38.4</v>
       </c>
       <c r="J12" t="n">
-        <v>86.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L12" t="n">
         <v>8.300000000000001</v>
@@ -2520,34 +2587,34 @@
         <v>24.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T12" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="W12" t="n">
         <v>7.8</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="AA12" t="n">
         <v>21.8</v>
@@ -2559,19 +2626,19 @@
         <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI12" t="n">
         <v>6</v>
@@ -2586,7 +2653,7 @@
         <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
         <v>12</v>
@@ -2601,7 +2668,7 @@
         <v>19</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
         <v>5</v>
@@ -2610,19 +2677,19 @@
         <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
         <v>5</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>30</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2771,7 +2838,7 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO13" t="n">
         <v>10</v>
@@ -2789,22 +2856,22 @@
         <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU13" t="n">
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY13" t="n">
         <v>23</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>22</v>
       </c>
       <c r="AZ13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.694</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -2866,25 +2933,25 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O14" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="P14" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R14" t="n">
         <v>10.9</v>
@@ -2893,16 +2960,16 @@
         <v>34.1</v>
       </c>
       <c r="T14" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>5.3</v>
@@ -2911,19 +2978,19 @@
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.4</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2953,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2977,19 +3044,19 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW14" t="n">
         <v>4</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -3027,67 +3094,67 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.27</v>
+        <v>0.278</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>80.7</v>
+        <v>80.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L15" t="n">
         <v>7.9</v>
       </c>
       <c r="M15" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O15" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.752</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T15" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="V15" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W15" t="n">
         <v>5.8</v>
       </c>
       <c r="X15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y15" t="n">
         <v>4.8</v>
@@ -3096,34 +3163,34 @@
         <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AB15" t="n">
         <v>100.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
         <v>11</v>
@@ -3135,16 +3202,16 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3153,16 +3220,16 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AU15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
         <v>6</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-6</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
@@ -3299,7 +3366,7 @@
         <v>29</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>24</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3326,7 +3393,7 @@
         <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR16" t="n">
         <v>28</v>
@@ -3344,7 +3411,7 @@
         <v>15</v>
       </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -3469,25 +3536,25 @@
         <v>-5.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG17" t="n">
         <v>21</v>
       </c>
-      <c r="AG17" t="n">
-        <v>20</v>
-      </c>
       <c r="AH17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
         <v>14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK17" t="n">
         <v>14</v>
@@ -3505,19 +3572,19 @@
         <v>26</v>
       </c>
       <c r="AP17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU17" t="n">
         <v>14</v>
@@ -3532,7 +3599,7 @@
         <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="AI18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
@@ -3681,7 +3748,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3696,19 +3763,19 @@
         <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX18" t="n">
         <v>26</v>
@@ -3720,7 +3787,7 @@
         <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>17</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>17</v>
@@ -3878,16 +3945,16 @@
         <v>17</v>
       </c>
       <c r="AS19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT19" t="n">
         <v>18</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>19</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>21</v>
@@ -3899,7 +3966,7 @@
         <v>6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -3937,58 +4004,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J20" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K20" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O20" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P20" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T20" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U20" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V20" t="n">
         <v>12.6</v>
@@ -3997,7 +4064,7 @@
         <v>7.7</v>
       </c>
       <c r="X20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="n">
         <v>4.5</v>
@@ -4006,16 +4073,16 @@
         <v>19.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4027,7 +4094,7 @@
         <v>7</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI20" t="n">
         <v>7</v>
@@ -4045,10 +4112,10 @@
         <v>7</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP20" t="n">
         <v>29</v>
@@ -4063,22 +4130,22 @@
         <v>15</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
         <v>27</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.278</v>
+        <v>0.257</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,7 +4204,7 @@
         <v>34.9</v>
       </c>
       <c r="J21" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K21" t="n">
         <v>0.435</v>
@@ -4146,34 +4213,34 @@
         <v>5.6</v>
       </c>
       <c r="M21" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.329</v>
+        <v>0.332</v>
       </c>
       <c r="O21" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P21" t="n">
         <v>26.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7</v>
+        <v>0.703</v>
       </c>
       <c r="R21" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T21" t="n">
         <v>42</v>
       </c>
       <c r="U21" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="V21" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="W21" t="n">
         <v>6.5</v>
@@ -4182,40 +4249,40 @@
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7</v>
+        <v>-7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF21" t="n">
         <v>26</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
@@ -4227,7 +4294,7 @@
         <v>18</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
         <v>14</v>
@@ -4236,25 +4303,25 @@
         <v>12</v>
       </c>
       <c r="AQ21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR21" t="n">
         <v>4</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>17</v>
@@ -4272,7 +4339,7 @@
         <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -4391,16 +4458,16 @@
         <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ22" t="n">
         <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL22" t="n">
         <v>2</v>
@@ -4439,7 +4506,7 @@
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
@@ -4579,7 +4646,7 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK23" t="n">
         <v>20</v>
@@ -4597,7 +4664,7 @@
         <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ23" t="n">
         <v>27</v>
@@ -4606,7 +4673,7 @@
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT23" t="n">
         <v>12</v>
@@ -4615,7 +4682,7 @@
         <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4770,7 +4837,7 @@
         <v>3</v>
       </c>
       <c r="AM24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN24" t="n">
         <v>4</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4806,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -4847,64 +4914,64 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
         <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>0.611</v>
+        <v>0.629</v>
       </c>
       <c r="H25" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="J25" t="n">
-        <v>78.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N25" t="n">
         <v>0.389</v>
       </c>
       <c r="O25" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P25" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R25" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S25" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T25" t="n">
-        <v>40.7</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
         <v>22</v>
       </c>
       <c r="V25" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W25" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="X25" t="n">
         <v>4.6</v>
@@ -4913,40 +4980,40 @@
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA25" t="n">
         <v>21.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>97.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AI25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>11</v>
@@ -4958,7 +5025,7 @@
         <v>2</v>
       </c>
       <c r="AO25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP25" t="n">
         <v>21</v>
@@ -4967,22 +5034,22 @@
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
         <v>12</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX25" t="n">
         <v>18</v>
@@ -4991,16 +5058,16 @@
         <v>1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
         <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -5107,25 +5174,25 @@
         <v>-2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>21</v>
       </c>
       <c r="AF26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>22</v>
       </c>
       <c r="AJ26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK26" t="n">
         <v>13</v>
@@ -5134,10 +5201,10 @@
         <v>19</v>
       </c>
       <c r="AM26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
@@ -5179,7 +5246,7 @@
         <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>5.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>15</v>
@@ -5310,7 +5377,7 @@
         <v>22</v>
       </c>
       <c r="AK27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL27" t="n">
         <v>5</v>
@@ -5322,13 +5389,13 @@
         <v>3</v>
       </c>
       <c r="AO27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
         <v>23</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR27" t="n">
         <v>23</v>
@@ -5337,7 +5404,7 @@
         <v>13</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
         <v>9</v>
@@ -5361,7 +5428,7 @@
         <v>19</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>-7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF28" t="n">
         <v>28</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>27</v>
       </c>
       <c r="AG28" t="n">
         <v>28</v>
@@ -5486,7 +5553,7 @@
         <v>18</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
         <v>6</v>
@@ -5510,10 +5577,10 @@
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5546,7 +5613,7 @@
         <v>18</v>
       </c>
       <c r="BC28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -5575,64 +5642,64 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
         <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.541</v>
+        <v>0.528</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="I29" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J29" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L29" t="n">
         <v>7.3</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N29" t="n">
         <v>0.407</v>
       </c>
       <c r="O29" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P29" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="R29" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S29" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U29" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V29" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="W29" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X29" t="n">
         <v>4.4</v>
@@ -5641,40 +5708,40 @@
         <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.3</v>
+        <v>96.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
         <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI29" t="n">
         <v>9</v>
       </c>
-      <c r="AI29" t="n">
-        <v>8</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5686,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP29" t="n">
         <v>30</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
@@ -5704,28 +5771,28 @@
         <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX29" t="n">
         <v>24</v>
       </c>
-      <c r="AX29" t="n">
-        <v>22</v>
-      </c>
       <c r="AY29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>9</v>
       </c>
       <c r="BA29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>4.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -5865,7 +5932,7 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5877,13 +5944,13 @@
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
         <v>29</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5898,7 +5965,7 @@
         <v>25</v>
       </c>
       <c r="AY30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>2.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF31" t="n">
         <v>10</v>
@@ -6029,10 +6096,10 @@
         <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6059,7 +6126,7 @@
         <v>3</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-13-2007-08</t>
+          <t>2008-01-13</t>
         </is>
       </c>
     </row>
